--- a/Team-Data/2013-14/12-12-2013-14.xlsx
+++ b/Team-Data/2013-14/12-12-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,13 +821,13 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>11</v>
@@ -769,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
         <v>20</v>
@@ -799,7 +866,7 @@
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -951,7 +1018,7 @@
         <v>23</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
@@ -966,7 +1033,7 @@
         <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>23</v>
@@ -993,7 +1060,7 @@
         <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,85 +1110,85 @@
         <v>34.4</v>
       </c>
       <c r="J4" t="n">
-        <v>78.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.437</v>
       </c>
       <c r="L4" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M4" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="N4" t="n">
-        <v>0.341</v>
+        <v>0.338</v>
       </c>
       <c r="O4" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="P4" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.762</v>
+        <v>0.753</v>
       </c>
       <c r="R4" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="S4" t="n">
-        <v>30.9</v>
+        <v>30.6</v>
       </c>
       <c r="T4" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U4" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V4" t="n">
         <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6.4</v>
+        <v>-7.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1133,22 +1200,22 @@
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP4" t="n">
         <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
         <v>22</v>
@@ -1157,25 +1224,25 @@
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
         <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
         <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1497,7 +1564,7 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO6" t="n">
         <v>14</v>
@@ -1509,7 +1576,7 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
         <v>21</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
         <v>8</v>
@@ -2046,7 +2113,7 @@
         <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2401,7 +2468,7 @@
         <v>5</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2443,7 +2510,7 @@
         <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -2481,85 +2548,85 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
         <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.652</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J12" t="n">
-        <v>79.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.474</v>
+        <v>0.477</v>
       </c>
       <c r="L12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="O12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="P12" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7</v>
+        <v>0.697</v>
       </c>
       <c r="R12" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S12" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="T12" t="n">
         <v>47.3</v>
       </c>
       <c r="U12" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="V12" t="n">
-        <v>17.8</v>
+        <v>18.3</v>
       </c>
       <c r="W12" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X12" t="n">
         <v>6.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>107.3</v>
+        <v>107.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,25 +2638,25 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,28 +2668,28 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
         <v>16</v>
@@ -2634,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2774,7 +2841,7 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2792,7 +2859,7 @@
         <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -2845,46 +2912,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
         <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.625</v>
+        <v>0.652</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>37.6</v>
+        <v>38.1</v>
       </c>
       <c r="J14" t="n">
-        <v>81.5</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.461</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M14" t="n">
         <v>23.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.326</v>
+        <v>0.329</v>
       </c>
       <c r="O14" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="P14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.703</v>
+        <v>0.705</v>
       </c>
       <c r="R14" t="n">
         <v>10.4</v>
@@ -2896,40 +2963,40 @@
         <v>42.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="V14" t="n">
         <v>14.5</v>
       </c>
       <c r="W14" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>103.3</v>
+        <v>103.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>7</v>
@@ -2938,10 +3005,10 @@
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AK14" t="n">
         <v>7</v>
@@ -2953,16 +3020,16 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -2974,19 +3041,19 @@
         <v>15</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ14" t="n">
         <v>27</v>
@@ -2995,10 +3062,10 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3120,7 +3187,7 @@
         <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
@@ -3156,7 +3223,7 @@
         <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3329,7 +3396,7 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3484,7 +3551,7 @@
         <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3502,13 +3569,13 @@
         <v>6</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3702,7 +3769,7 @@
         <v>28</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>12</v>
@@ -3848,7 +3915,7 @@
         <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3881,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -3908,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4115,7 @@
         <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP20" t="n">
         <v>12</v>
@@ -4081,13 +4148,13 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA20" t="n">
         <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-4</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>27</v>
@@ -4239,7 +4306,7 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4260,7 +4327,7 @@
         <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4409,7 +4476,7 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4424,7 +4491,7 @@
         <v>14</v>
       </c>
       <c r="AS22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>2</v>
@@ -4454,7 +4521,7 @@
         <v>4</v>
       </c>
       <c r="BC22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
         <v>26</v>
@@ -4600,7 +4667,7 @@
         <v>24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4618,7 +4685,7 @@
         <v>25</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>16</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-7.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF24" t="n">
         <v>28</v>
@@ -4779,10 +4846,10 @@
         <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR24" t="n">
         <v>10</v>
@@ -4797,7 +4864,7 @@
         <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW24" t="n">
         <v>9</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
       </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="n">
         <v>9</v>
@@ -4940,10 +5007,10 @@
         <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
         <v>6</v>
@@ -4961,7 +5028,7 @@
         <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ25" t="n">
         <v>18</v>
@@ -4982,7 +5049,7 @@
         <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.826</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
@@ -5047,70 +5114,70 @@
         <v>39.2</v>
       </c>
       <c r="J26" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L26" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M26" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.409</v>
+        <v>0.415</v>
       </c>
       <c r="O26" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="P26" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S26" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T26" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="U26" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V26" t="n">
         <v>14.3</v>
       </c>
       <c r="W26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.4</v>
+        <v>106.2</v>
       </c>
       <c r="AC26" t="n">
         <v>6.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
         <v>4</v>
@@ -5128,7 +5195,7 @@
         <v>4</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
         <v>4</v>
@@ -5140,22 +5207,22 @@
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS26" t="n">
         <v>10</v>
       </c>
       <c r="AT26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU26" t="n">
         <v>8</v>
@@ -5167,10 +5234,10 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>3</v>
@@ -5182,7 +5249,7 @@
         <v>2</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5398,7 @@
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>10</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5531,10 +5598,10 @@
         <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -5656,13 +5723,13 @@
         <v>26</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
@@ -5713,7 +5780,7 @@
         <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -5865,13 +5932,13 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
         <v>18</v>
       </c>
       <c r="AP30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ30" t="n">
         <v>21</v>
@@ -5901,7 +5968,7 @@
         <v>17</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6126,7 @@
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
@@ -6080,7 +6147,7 @@
         <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-12-2013-14</t>
+          <t>2013-12-12</t>
         </is>
       </c>
     </row>
